--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,22 +464,22 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
+          <t>Camb - Height Adjustable table -  SP - BM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>235.67</v>
+        <v>133.76</v>
       </c>
       <c r="E2" t="n">
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>2962</v>
+        <v>2342</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -492,22 +492,22 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
+          <t>Camb - Height Adjustable table -  SP - BM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>273.7</v>
+        <v>46.14</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>328</v>
+        <v>492</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -520,22 +520,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-KT-Phrase</t>
+          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50.23</v>
+        <v>642.73</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>621</v>
+        <v>8262</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -548,50 +548,50 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-KT-Phrase</t>
+          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56.19</v>
+        <v>1888.48</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>359</v>
+        <v>6390</v>
       </c>
       <c r="G5" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-PT-Exact</t>
+          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55.72</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>259</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -604,22 +604,22 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-PT-Exact</t>
+          <t>Camb-Height Adjustable table-KT-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.39</v>
+        <v>43.52</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>430</v>
+        <v>286</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -632,22 +632,22 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-Motorized-SP-PT-Exact</t>
+          <t>Camb-Height Adjustable table-KT-Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>175.93</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1463</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -660,78 +660,78 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-Motorized-SP-PT-Exact</t>
+          <t>Camb-Lshape-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>287.66</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>3431</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Lshape-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26.18</v>
+        <v>349.82</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>205</v>
+        <v>1658</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>14150.84</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Lshape-SP-PT-Exact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>679.35</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>3408</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Lshape-SP-PT-Exact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -753,41 +753,41 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.09</v>
+        <v>265.54</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>205</v>
+        <v>1866</v>
       </c>
       <c r="G12" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized desk- B0DQ4YWSMC - PT 02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>84.2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>832</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -800,22 +800,22 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized desk-B0DQ4YWSMC - BM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>157.71</v>
+        <v>22.85</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>833</v>
+        <v>552</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized desk-B0DQ4YWSMC - Exact</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>153</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -856,22 +856,22 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
+          <t>Camb-Motorized desk-B0DQ4YWSMC- Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>310.9</v>
+        <v>36.06</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>1090</v>
+        <v>312</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -884,22 +884,22 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
+          <t>Camb-Motorized sit stand-B0DQ4YWSMC- PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>257.23</v>
+        <v>12.02</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>2157</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -912,50 +912,50 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-Motorized-SP-KT-BM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>251.17</v>
+        <v>2302.74</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
-        <v>829</v>
+        <v>21703</v>
       </c>
       <c r="G18" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>389.17</v>
+        <v>857.95</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
-        <v>10067</v>
+        <v>4221</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -968,22 +968,22 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>86.12</v>
+        <v>56.36</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP- L Shaped-B0BFWD6SNF- Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>259.67</v>
+        <v>11.53</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>3038</v>
+        <v>421</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP- L Shaped-B0BFWD6SNF-BM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1033,41 +1033,41 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.93</v>
+        <v>280.8</v>
       </c>
       <c r="E22" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1972</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7456.78</v>
+      </c>
+      <c r="H22" t="n">
         <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1021</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>257.72</v>
+        <v>10.3</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>668</v>
+        <v>435</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,134 +1080,134 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP- L Shaped-B0BFWD6SNF-PT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>490.35</v>
+        <v>111.59</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>1903</v>
+        <v>1616</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>7456.78</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>360.52</v>
+        <v>127.85</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>1826</v>
+        <v>2512</v>
       </c>
       <c r="G25" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>278.87</v>
+        <v>139.15</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>1838</v>
+        <v>696</v>
       </c>
       <c r="G26" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>232.92</v>
+        <v>196.04</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>920</v>
+        <v>1130</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>323.49</v>
+        <v>217.43</v>
       </c>
       <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>899</v>
+        <v>3447</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1220,50 +1220,50 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>505.65</v>
+        <v>636.09</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F29" t="n">
-        <v>6816</v>
+        <v>5325</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>12712.71</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>226.56</v>
+        <v>95.64</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>2160</v>
+        <v>752</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.05</v>
+        <v>1771.84</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="F31" t="n">
-        <v>792</v>
+        <v>9575</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1304,63 +1304,63 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1185.81</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F32" t="n">
-        <v>179</v>
+        <v>15794</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>36902.54</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>23.86</v>
+        <v>784.6899999999999</v>
       </c>
       <c r="E33" t="n">
+        <v>28</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2870</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7075.42</v>
+      </c>
+      <c r="H33" t="n">
         <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>334</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>70.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>498</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1388,78 +1388,78 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>180.01</v>
+        <v>1945.77</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F35" t="n">
-        <v>626</v>
+        <v>31902</v>
       </c>
       <c r="G35" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>158.49</v>
+        <v>502.97</v>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F36" t="n">
-        <v>1275</v>
+        <v>4725</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1284.49</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>16106</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,22 +1472,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>282.93</v>
+        <v>124.61</v>
       </c>
       <c r="E38" t="n">
         <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>379</v>
+        <v>3377</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1500,22 +1500,22 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WB- SP-B0DP3194QN-PT</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- BM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.86</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2361</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,22 +1528,22 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>296.96</v>
+        <v>713.51</v>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F40" t="n">
-        <v>1147</v>
+        <v>2224</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,50 +1556,50 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact - 01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>189.51</v>
+        <v>40.5</v>
       </c>
       <c r="E41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>921</v>
+        <v>431</v>
       </c>
       <c r="G41" t="n">
-        <v>2533.9</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C-PT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>208.94</v>
+        <v>63.67</v>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>2180</v>
+        <v>720</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,22 +1612,22 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>405.05</v>
+        <v>2050</v>
       </c>
       <c r="E43" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="F43" t="n">
-        <v>4440</v>
+        <v>6896</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,22 +1640,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2235.34</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>12060</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,106 +1668,106 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>259.97</v>
+        <v>1721</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="F45" t="n">
-        <v>1227</v>
+        <v>8613</v>
       </c>
       <c r="G45" t="n">
-        <v>2626.27</v>
+        <v>14489.83</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1519.79</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>17149</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>21777.12</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>898.74</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>4305</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>7287.28</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1301.18</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3808</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,78 +1780,78 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>272.81</v>
+        <v>2571.91</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>243</v>
       </c>
       <c r="F49" t="n">
-        <v>844</v>
+        <v>34909</v>
       </c>
       <c r="G49" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1472.83</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>10188</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>7287.29</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>196.01</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>3495</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>127.84</v>
+        <v>58.91</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>2796</v>
+        <v>1312</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1892,22 +1892,22 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>174.91</v>
+        <v>99.47</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>4733</v>
+        <v>843</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1920,22 +1920,22 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>144.66</v>
+        <v>740.28</v>
       </c>
       <c r="E54" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F54" t="n">
-        <v>1439</v>
+        <v>5907</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1948,50 +1948,50 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>281.29</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>2493</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>174.99</v>
+        <v>309.71</v>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
-        <v>911</v>
+        <v>1960</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,35 +2004,35 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>42.83</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2060,7 +2060,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2069,13 +2069,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>281.66</v>
+        <v>1079.68</v>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F59" t="n">
-        <v>1444</v>
+        <v>1276</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WB- SP-B0DP3194QN-PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>286.43</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>2789</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,78 +2116,78 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>259.94</v>
+        <v>1234.79</v>
       </c>
       <c r="E61" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F61" t="n">
-        <v>4495</v>
+        <v>5393</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>127.59</v>
+        <v>1647.39</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>216</v>
+        <v>2480</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>23533.9</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>135.2</v>
+        <v>1011.82</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>214</v>
+        <v>5879</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,50 +2200,50 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>30.45</v>
+        <v>1259.25</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="F64" t="n">
-        <v>202</v>
+        <v>11027</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>5082.21</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>30.84</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2256,25 +2256,25 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>93.95999999999999</v>
+        <v>1312.49</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>435</v>
+        <v>5108</v>
       </c>
       <c r="G66" t="n">
-        <v>1694.07</v>
+        <v>2626.27</v>
       </c>
       <c r="H66" t="n">
         <v>1</v>
@@ -2284,12 +2284,12 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,22 +2312,22 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>23.22</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2340,22 +2340,22 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>642</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,50 +2368,50 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1285.22</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F70" t="n">
-        <v>485</v>
+        <v>3832</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.02</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2424,25 +2424,25 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>43.62</v>
+        <v>632.78</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F72" t="n">
-        <v>616</v>
+        <v>8964</v>
       </c>
       <c r="G72" t="n">
-        <v>3643.22</v>
+        <v>2783.9</v>
       </c>
       <c r="H72" t="n">
         <v>1</v>
@@ -2452,12 +2452,12 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2480,25 +2480,25 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>69.44</v>
+        <v>620.4300000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>547</v>
+        <v>16201</v>
       </c>
       <c r="G74" t="n">
-        <v>1694.06</v>
+        <v>2783.9</v>
       </c>
       <c r="H74" t="n">
         <v>1</v>
@@ -2508,22 +2508,22 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>27.79</v>
+        <v>174.91</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F75" t="n">
-        <v>761</v>
+        <v>4732</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2536,22 +2536,22 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>850.21</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F76" t="n">
-        <v>62</v>
+        <v>7602</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,22 +2564,22 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>263.66</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>1005</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2601,59 +2601,59 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>259.63</v>
+        <v>560.4000000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F78" t="n">
-        <v>1012</v>
+        <v>3646</v>
       </c>
       <c r="G78" t="n">
-        <v>2372.03</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>300.03</v>
+        <v>475.54</v>
       </c>
       <c r="E79" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F79" t="n">
-        <v>3040</v>
+        <v>5707</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>4955.93</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2676,78 +2676,78 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>112.29</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>1355</v>
+        <v>2336</v>
       </c>
       <c r="G81" t="n">
-        <v>490.68</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>140.82</v>
+        <v>1081.5</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F82" t="n">
-        <v>472</v>
+        <v>10986</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1450.85</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6.51</v>
+        <v>1245.54</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="F83" t="n">
-        <v>230</v>
+        <v>20600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2760,106 +2760,106 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>29.26</v>
+        <v>1841.09</v>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="F84" t="n">
-        <v>401</v>
+        <v>26611</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>6988.98</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>603.23</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F85" t="n">
-        <v>145</v>
+        <v>2272</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>5082.21</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>142.7</v>
+        <v>486.51</v>
       </c>
       <c r="E86" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F86" t="n">
-        <v>527</v>
+        <v>1909</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>77.3</v>
+        <v>428.21</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F87" t="n">
-        <v>104</v>
+        <v>1219</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,22 +2872,22 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>190.31</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>3374</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2900,25 +2900,25 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>256.2</v>
+        <v>445.12</v>
       </c>
       <c r="E89" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>4393</v>
+        <v>2331</v>
       </c>
       <c r="G89" t="n">
-        <v>981.36</v>
+        <v>1694.07</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -2928,22 +2928,22 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>373.51</v>
+        <v>61.01</v>
       </c>
       <c r="E90" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>9595</v>
+        <v>1249</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2956,27 +2956,811 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>White Mulberry-Motorized-SP-KT-BM</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>317.39</v>
+        <v>23.22</v>
       </c>
       <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>496</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Branded</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2284</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Branded</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1771</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="E94" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" t="n">
+        <v>548</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>273.89</v>
+      </c>
+      <c r="E95" t="n">
+        <v>20</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2765</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3643.22</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>82.81999999999999</v>
+      </c>
+      <c r="E96" t="n">
+        <v>6</v>
+      </c>
+      <c r="F96" t="n">
+        <v>609</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>335.06</v>
+      </c>
+      <c r="E97" t="n">
+        <v>26</v>
+      </c>
+      <c r="F97" t="n">
+        <v>3334</v>
+      </c>
+      <c r="G97" t="n">
+        <v>5082.19</v>
+      </c>
+      <c r="H97" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>174.46</v>
+      </c>
+      <c r="E98" t="n">
         <v>14</v>
       </c>
-      <c r="F91" t="n">
-        <v>4224</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
+      <c r="F98" t="n">
+        <v>3237</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>575</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>642.13</v>
+      </c>
+      <c r="E100" t="n">
+        <v>40</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3289</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>917.61</v>
+      </c>
+      <c r="E101" t="n">
+        <v>44</v>
+      </c>
+      <c r="F101" t="n">
+        <v>6810</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2372.03</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1262.63</v>
+      </c>
+      <c r="E102" t="n">
+        <v>64</v>
+      </c>
+      <c r="F102" t="n">
+        <v>13774</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>WM-SP-POS stand- Multi - PT</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>609.1500000000001</v>
+      </c>
+      <c r="E104" t="n">
+        <v>38</v>
+      </c>
+      <c r="F104" t="n">
+        <v>7135</v>
+      </c>
+      <c r="G104" t="n">
+        <v>981.36</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>344.06</v>
+      </c>
+      <c r="E105" t="n">
+        <v>21</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2885</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1778.81</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1243</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>188.36</v>
+      </c>
+      <c r="E108" t="n">
+        <v>21</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2794</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1472.04</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="n">
+        <v>954</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1214.12</v>
+      </c>
+      <c r="E110" t="n">
+        <v>48</v>
+      </c>
+      <c r="F110" t="n">
+        <v>4405</v>
+      </c>
+      <c r="G110" t="n">
+        <v>981.36</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>287.62</v>
+      </c>
+      <c r="E111" t="n">
+        <v>12</v>
+      </c>
+      <c r="F111" t="n">
+        <v>746</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>873.84</v>
+      </c>
+      <c r="E113" t="n">
+        <v>69</v>
+      </c>
+      <c r="F113" t="n">
+        <v>16306</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2326.28</v>
+      </c>
+      <c r="H113" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1572.32</v>
+      </c>
+      <c r="E114" t="n">
+        <v>65</v>
+      </c>
+      <c r="F114" t="n">
+        <v>34407</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>White Mulberry Height Adjustable Table-B0CPT3Q25C-B0DQ4YWSMC-SP-BM</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>10</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>White Mulberry Height Adjustable Table-B0CPT3Q25C-SP-Phrase</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>White Mulberry Height Adjustable Table-Phrase-SP</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5W4TCP-SP-Phrase</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>251.92</v>
+      </c>
+      <c r="E118" t="n">
+        <v>17</v>
+      </c>
+      <c r="F118" t="n">
+        <v>7734</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1450.85</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>White Mulberry-Dual Monitor Arm-B0DB5VVPSB-PT-SP</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>573.48</v>
+      </c>
+      <c r="E119" t="n">
+        <v>38</v>
+      </c>
+      <c r="F119" t="n">
+        <v>5498</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3273,13 +4057,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.77</v>
+        <v>67.09</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>377</v>
+        <v>5649</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3301,13 +4085,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>57.48</v>
+        <v>396.65</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>1109</v>
+        <v>12300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3385,13 +4169,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53.16</v>
+        <v>419.26</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>2074</v>
+        <v>13863</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -3413,13 +4197,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>131.5</v>
+        <v>372.86</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>1841</v>
+        <v>17109</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -3439,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3502,13 +4286,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.333333333333333</v>
+        <v>9.603333333333333</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3535,13 +4319,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.333333333333333</v>
+        <v>9.603333333333333</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3568,13 +4352,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1.333333333333333</v>
+        <v>9.603333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3601,13 +4385,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1.333333333333333</v>
+        <v>9.603333333333333</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3634,13 +4418,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.333333333333333</v>
+        <v>9.603333333333333</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3667,13 +4451,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.333333333333333</v>
+        <v>9.603333333333333</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3700,16 +4484,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1394</v>
+        <v>4866</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="F8" t="n">
-        <v>138.01</v>
+        <v>480.99</v>
       </c>
       <c r="G8" t="n">
-        <v>10676.69</v>
+        <v>18048.725</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -3733,16 +4517,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1394</v>
+        <v>4866</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="F9" t="n">
-        <v>138.01</v>
+        <v>480.99</v>
       </c>
       <c r="G9" t="n">
-        <v>10676.69</v>
+        <v>18048.725</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -3766,16 +4550,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>532</v>
+        <v>2196</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
-        <v>79.8</v>
+        <v>297.6666666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4237.57</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -3799,16 +4583,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>532</v>
+        <v>2196</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>79.8</v>
+        <v>297.6666666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>4237.57</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3832,16 +4616,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>532</v>
+        <v>2196</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
-        <v>79.8</v>
+        <v>297.6666666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4237.57</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -3865,19 +4649,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>266</v>
+        <v>1942</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>64.0625</v>
+        <v>321.02</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5306.565</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3898,19 +4682,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>266</v>
+        <v>1942</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>64.0625</v>
+        <v>321.02</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5306.565</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3931,19 +4715,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>266</v>
+        <v>1942</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>64.0625</v>
+        <v>321.02</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>5306.565</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3964,19 +4748,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>266</v>
+        <v>1942</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F16" t="n">
-        <v>64.0625</v>
+        <v>321.02</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5306.565</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3997,13 +4781,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1416</v>
+        <v>5925</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
-        <v>192.01</v>
+        <v>655.9400000000001</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4030,19 +4814,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1788</v>
+        <v>10810</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="F18" t="n">
-        <v>369.7</v>
+        <v>1717.92</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>5567.8</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4054,30 +4838,228 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2366</v>
+      </c>
+      <c r="E19" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" t="n">
+        <v>203.86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.922404316345447</v>
+      </c>
+      <c r="G20" t="n">
+        <v>949.1964943859526</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10.06759568365455</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1380.463505614047</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9690</v>
+      </c>
+      <c r="E22" t="n">
+        <v>92</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1496.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4955.93</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2180</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>1538</v>
-      </c>
-      <c r="E19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F19" t="n">
-        <v>269.2</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="D24" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34</v>
+      </c>
+      <c r="F24" t="n">
+        <v>386.03</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6498</v>
+      </c>
+      <c r="E25" t="n">
+        <v>52</v>
+      </c>
+      <c r="F25" t="n">
+        <v>580.3499999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>642.73</v>
+        <v>784.0999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>8262</v>
+        <v>10060</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1888.48</v>
+        <v>3097.71</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="F5" t="n">
-        <v>6390</v>
+        <v>9526</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>682</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>287.66</v>
+        <v>463.22</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>3431</v>
+        <v>5039</v>
       </c>
       <c r="G9" t="n">
         <v>7075.42</v>
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>349.82</v>
+        <v>558.1799999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>1658</v>
+        <v>2236</v>
       </c>
       <c r="G10" t="n">
         <v>14150.84</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>679.35</v>
+        <v>963.85</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>3408</v>
+        <v>5063</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>265.54</v>
+        <v>590.05</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F12" t="n">
-        <v>1866</v>
+        <v>3061</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>480</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22.85</v>
+        <v>110.98</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>552</v>
+        <v>1559</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>36.06</v>
+        <v>77.2</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>312</v>
+        <v>1166</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.02</v>
+        <v>395.98</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>6007</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -921,19 +921,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2302.74</v>
+        <v>3392.61</v>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="F18" t="n">
-        <v>21703</v>
+        <v>30841</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>12712.71</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.53</v>
+        <v>46.56</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>421</v>
+        <v>960</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>280.8</v>
+        <v>697.58</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>1972</v>
+        <v>7837</v>
       </c>
       <c r="G22" t="n">
         <v>7456.78</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.3</v>
+        <v>40.86</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>435</v>
+        <v>1448</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>111.59</v>
+        <v>428.24</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F24" t="n">
-        <v>1616</v>
+        <v>5864</v>
       </c>
       <c r="G24" t="n">
-        <v>7456.78</v>
+        <v>21607.62</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>127.85</v>
+        <v>213.97</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>2512</v>
+        <v>5524</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>139.15</v>
+        <v>199.23</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>696</v>
+        <v>1217</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>196.04</v>
+        <v>228.02</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>1130</v>
+        <v>1469</v>
       </c>
       <c r="G27" t="n">
         <v>7075.42</v>
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>217.43</v>
+        <v>271.19</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>3447</v>
+        <v>4514</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>636.09</v>
+        <v>858.98</v>
       </c>
       <c r="E29" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>5325</v>
+        <v>8103</v>
       </c>
       <c r="G29" t="n">
         <v>12712.71</v>
@@ -1257,19 +1257,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>95.64</v>
+        <v>207.47</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>752</v>
+        <v>1155</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>7287.29</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1771.84</v>
+        <v>2482.98</v>
       </c>
       <c r="E31" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F31" t="n">
-        <v>9575</v>
+        <v>13656</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1185.81</v>
+        <v>1550.91</v>
       </c>
       <c r="E32" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="F32" t="n">
-        <v>15794</v>
+        <v>18142</v>
       </c>
       <c r="G32" t="n">
         <v>36902.54</v>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>784.6899999999999</v>
+        <v>1036.75</v>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>2870</v>
+        <v>4336</v>
       </c>
       <c r="G33" t="n">
         <v>7075.42</v>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1945.77</v>
+        <v>2653.69</v>
       </c>
       <c r="E35" t="n">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="F35" t="n">
-        <v>31902</v>
+        <v>44557</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>502.97</v>
+        <v>593.87</v>
       </c>
       <c r="E36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F36" t="n">
-        <v>4725</v>
+        <v>5972</v>
       </c>
       <c r="G36" t="n">
         <v>7075.42</v>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1284.49</v>
+        <v>1791.87</v>
       </c>
       <c r="E37" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F37" t="n">
-        <v>16106</v>
+        <v>22616</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>124.61</v>
+        <v>245.5</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>3377</v>
+        <v>4641</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>347.86</v>
+        <v>1248.88</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="F39" t="n">
-        <v>2361</v>
+        <v>11996</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>713.51</v>
+        <v>1607.59</v>
       </c>
       <c r="E40" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>2224</v>
+        <v>10557</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>40.5</v>
+        <v>164.29</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
-        <v>431</v>
+        <v>1642</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>63.67</v>
+        <v>517.1900000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="F42" t="n">
-        <v>720</v>
+        <v>4911</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2050</v>
+        <v>3169.08</v>
       </c>
       <c r="E43" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="F43" t="n">
-        <v>6896</v>
+        <v>8652</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2235.34</v>
+        <v>3008.38</v>
       </c>
       <c r="E44" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="F44" t="n">
-        <v>12060</v>
+        <v>13905</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1721</v>
+        <v>2096.32</v>
       </c>
       <c r="E45" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="F45" t="n">
-        <v>8613</v>
+        <v>10523</v>
       </c>
       <c r="G45" t="n">
         <v>14489.83</v>
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1519.79</v>
+        <v>2034.34</v>
       </c>
       <c r="E46" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="F46" t="n">
-        <v>17149</v>
+        <v>20137</v>
       </c>
       <c r="G46" t="n">
         <v>21777.12</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>898.74</v>
+        <v>1315.22</v>
       </c>
       <c r="E47" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F47" t="n">
-        <v>4305</v>
+        <v>5984</v>
       </c>
       <c r="G47" t="n">
         <v>7287.28</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1301.18</v>
+        <v>1811.46</v>
       </c>
       <c r="E48" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>3808</v>
+        <v>5288</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2571.91</v>
+        <v>3584.91</v>
       </c>
       <c r="E49" t="n">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="F49" t="n">
-        <v>34909</v>
+        <v>46677</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1472.83</v>
+        <v>1948.81</v>
       </c>
       <c r="E50" t="n">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="F50" t="n">
-        <v>10188</v>
+        <v>12768</v>
       </c>
       <c r="G50" t="n">
         <v>7287.29</v>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>58.91</v>
+        <v>85.48</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>1312</v>
+        <v>1362</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>99.47</v>
+        <v>112.86</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>843</v>
+        <v>942</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>740.28</v>
+        <v>1085.45</v>
       </c>
       <c r="E54" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>5907</v>
+        <v>9424</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>281.29</v>
+        <v>468.96</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F55" t="n">
-        <v>2493</v>
+        <v>3462</v>
       </c>
       <c r="G55" t="n">
         <v>7075.42</v>
@@ -2069,19 +2069,19 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1079.68</v>
+        <v>1578.69</v>
       </c>
       <c r="E59" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F59" t="n">
-        <v>1276</v>
+        <v>1791</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2626.28</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2125,19 +2125,19 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1234.79</v>
+        <v>1526.14</v>
       </c>
       <c r="E61" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F61" t="n">
-        <v>5393</v>
+        <v>7577</v>
       </c>
       <c r="G61" t="n">
-        <v>1694.07</v>
+        <v>3388.14</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2153,19 +2153,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1647.39</v>
+        <v>2382.73</v>
       </c>
       <c r="E62" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F62" t="n">
-        <v>2480</v>
+        <v>3271</v>
       </c>
       <c r="G62" t="n">
-        <v>23533.9</v>
+        <v>32847.46</v>
       </c>
       <c r="H62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1011.82</v>
+        <v>1161.34</v>
       </c>
       <c r="E63" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F63" t="n">
-        <v>5879</v>
+        <v>6612</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1259.25</v>
+        <v>1767.59</v>
       </c>
       <c r="E64" t="n">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="F64" t="n">
-        <v>11027</v>
+        <v>15094</v>
       </c>
       <c r="G64" t="n">
-        <v>5082.21</v>
+        <v>5082.209999999999</v>
       </c>
       <c r="H64" t="n">
         <v>3</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1312.49</v>
+        <v>2067.74</v>
       </c>
       <c r="E66" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="F66" t="n">
-        <v>5108</v>
+        <v>8689</v>
       </c>
       <c r="G66" t="n">
         <v>2626.27</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1285.22</v>
+        <v>1892.4</v>
       </c>
       <c r="E70" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>3832</v>
+        <v>10692</v>
       </c>
       <c r="G70" t="n">
         <v>2329.66</v>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>632.78</v>
+        <v>774.46</v>
       </c>
       <c r="E72" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
-        <v>8964</v>
+        <v>9391</v>
       </c>
       <c r="G72" t="n">
         <v>2783.9</v>
@@ -2495,7 +2495,7 @@
         <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>16201</v>
+        <v>16197</v>
       </c>
       <c r="G74" t="n">
         <v>2783.9</v>
@@ -2523,7 +2523,7 @@
         <v>11</v>
       </c>
       <c r="F75" t="n">
-        <v>4732</v>
+        <v>4727</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>850.21</v>
+        <v>987.9399999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F76" t="n">
-        <v>7602</v>
+        <v>8743</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>29</v>
       </c>
       <c r="F78" t="n">
-        <v>3646</v>
+        <v>3654</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>475.54</v>
+        <v>859.49</v>
       </c>
       <c r="E79" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F79" t="n">
-        <v>5707</v>
+        <v>8322</v>
       </c>
       <c r="G79" t="n">
         <v>4955.93</v>
@@ -2691,7 +2691,7 @@
         <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>2336</v>
+        <v>3737</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2713,19 +2713,19 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1081.5</v>
+        <v>1647.88</v>
       </c>
       <c r="E82" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F82" t="n">
-        <v>10986</v>
+        <v>15066</v>
       </c>
       <c r="G82" t="n">
-        <v>1450.85</v>
+        <v>6703.389999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1245.54</v>
+        <v>1946.09</v>
       </c>
       <c r="E83" t="n">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="F83" t="n">
-        <v>20600</v>
+        <v>30807</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2769,19 +2769,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1841.09</v>
+        <v>2396.04</v>
       </c>
       <c r="E84" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="F84" t="n">
-        <v>26611</v>
+        <v>32623</v>
       </c>
       <c r="G84" t="n">
-        <v>6988.98</v>
+        <v>11648.3</v>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>603.23</v>
+        <v>837.66</v>
       </c>
       <c r="E85" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F85" t="n">
-        <v>2272</v>
+        <v>3391</v>
       </c>
       <c r="G85" t="n">
         <v>5082.21</v>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>486.51</v>
+        <v>653.48</v>
       </c>
       <c r="E86" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F86" t="n">
-        <v>1909</v>
+        <v>2443</v>
       </c>
       <c r="G86" t="n">
         <v>1694.07</v>
@@ -2887,7 +2887,7 @@
         <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>3374</v>
+        <v>3930</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>2331</v>
+        <v>3369</v>
       </c>
       <c r="G89" t="n">
         <v>1694.07</v>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>61.01</v>
+        <v>131.49</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F90" t="n">
-        <v>1249</v>
+        <v>2000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>23.22</v>
+        <v>33.22</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>496</v>
+        <v>651</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2993,13 +2993,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>93.88</v>
+        <v>75.62</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>2284</v>
+        <v>2299</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>17.02</v>
+        <v>47.2</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>1771</v>
+        <v>2542</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>548</v>
+        <v>901</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3077,13 +3077,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>273.89</v>
+        <v>361.31</v>
       </c>
       <c r="E95" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F95" t="n">
-        <v>2765</v>
+        <v>4161</v>
       </c>
       <c r="G95" t="n">
         <v>3643.22</v>
@@ -3105,13 +3105,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>82.81999999999999</v>
+        <v>122.2</v>
       </c>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F96" t="n">
-        <v>609</v>
+        <v>874</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3133,13 +3133,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>335.06</v>
+        <v>585.62</v>
       </c>
       <c r="E97" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F97" t="n">
-        <v>3334</v>
+        <v>4778</v>
       </c>
       <c r="G97" t="n">
         <v>5082.19</v>
@@ -3167,7 +3167,7 @@
         <v>14</v>
       </c>
       <c r="F98" t="n">
-        <v>3237</v>
+        <v>3240</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>575</v>
+        <v>791</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>3289</v>
+        <v>3301</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3245,19 +3245,19 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>917.61</v>
+        <v>992.4300000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F101" t="n">
-        <v>6810</v>
+        <v>7144</v>
       </c>
       <c r="G101" t="n">
-        <v>2372.03</v>
+        <v>4744.06</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1262.63</v>
+        <v>1299.32</v>
       </c>
       <c r="E102" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F102" t="n">
-        <v>13774</v>
+        <v>14024</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3329,19 +3329,19 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>609.1500000000001</v>
+        <v>989.3800000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F104" t="n">
-        <v>7135</v>
+        <v>10609</v>
       </c>
       <c r="G104" t="n">
-        <v>981.36</v>
+        <v>2453.4</v>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>344.06</v>
+        <v>557.89</v>
       </c>
       <c r="E105" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F105" t="n">
-        <v>2885</v>
+        <v>5214</v>
       </c>
       <c r="G105" t="n">
         <v>1778.81</v>
@@ -3385,13 +3385,13 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>18.98</v>
+        <v>51.82</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F106" t="n">
-        <v>1243</v>
+        <v>2292</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3441,19 +3441,19 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>188.36</v>
+        <v>470.89</v>
       </c>
       <c r="E108" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F108" t="n">
-        <v>2794</v>
+        <v>4841</v>
       </c>
       <c r="G108" t="n">
-        <v>1472.04</v>
+        <v>2580.52</v>
       </c>
       <c r="H108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -3469,19 +3469,19 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>14.18</v>
+        <v>39.11</v>
       </c>
       <c r="E109" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1823</v>
+      </c>
+      <c r="G109" t="n">
+        <v>617.8</v>
+      </c>
+      <c r="H109" t="n">
         <v>1</v>
-      </c>
-      <c r="F109" t="n">
-        <v>954</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3497,19 +3497,19 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1214.12</v>
+        <v>2020.17</v>
       </c>
       <c r="E110" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="F110" t="n">
-        <v>4405</v>
+        <v>6055</v>
       </c>
       <c r="G110" t="n">
-        <v>981.36</v>
+        <v>2580.52</v>
       </c>
       <c r="H110" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>287.62</v>
+        <v>403.57</v>
       </c>
       <c r="E111" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F111" t="n">
-        <v>746</v>
+        <v>1141</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3577,58 +3577,58 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>873.84</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>16306</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>2326.28</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1572.32</v>
+        <v>1407.41</v>
       </c>
       <c r="E114" t="n">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="F114" t="n">
-        <v>34407</v>
+        <v>20444</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>4652.56</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table-B0CPT3Q25C-B0DQ4YWSMC-SP-BM</t>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1827.38</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F115" t="n">
-        <v>10</v>
+        <v>36421</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table-B0CPT3Q25C-SP-Phrase</t>
+          <t>White Mulberry Height Adjustable Table-B0CPT3Q25C-B0DQ4YWSMC-SP-BM</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table-Phrase-SP</t>
+          <t>White Mulberry Height Adjustable Table-B0CPT3Q25C-SP-Phrase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3712,55 +3712,83 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5W4TCP-SP-Phrase</t>
+          <t>White Mulberry Height Adjustable Table-Phrase-SP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>251.92</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>7734</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>1450.85</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
+          <t>White Mulberry Monitor Arm-B0DB5W4TCP-SP-Phrase</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>471.48</v>
+      </c>
+      <c r="E119" t="n">
+        <v>32</v>
+      </c>
+      <c r="F119" t="n">
+        <v>15158</v>
+      </c>
+      <c r="G119" t="n">
+        <v>3144.92</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>White Mulberry-Dual Monitor Arm-B0DB5VVPSB-PT-SP</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>B0DB5VVPSB</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>573.48</v>
-      </c>
-      <c r="E119" t="n">
-        <v>38</v>
-      </c>
-      <c r="F119" t="n">
-        <v>5498</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
+      <c r="D120" t="n">
+        <v>1091.45</v>
+      </c>
+      <c r="E120" t="n">
+        <v>67</v>
+      </c>
+      <c r="F120" t="n">
+        <v>8151</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4057,13 +4085,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>67.09</v>
+        <v>273.48</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>5649</v>
+        <v>10523</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4085,19 +4113,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>396.65</v>
+        <v>787.15</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>12300</v>
+        <v>23410</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1450.85</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -4175,7 +4203,7 @@
         <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>13863</v>
+        <v>14144</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4197,13 +4225,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>372.86</v>
+        <v>797.5</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="F15" t="n">
-        <v>17109</v>
+        <v>30782</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4223,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4277,28 +4305,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>8068</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>9.603333333333333</v>
+        <v>922.1800000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2626.28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4310,28 +4338,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>13719</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="F3" t="n">
-        <v>9.603333333333333</v>
+        <v>2366.55</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>8351.700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4343,22 +4371,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>8961</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>9.603333333333333</v>
+        <v>918.96</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4376,28 +4404,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9.603333333333333</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4409,28 +4437,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>6145</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>9.603333333333333</v>
+        <v>937.2172168694875</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3424.775491058187</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4442,28 +4470,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>6928</v>
       </c>
       <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1056.542783130512</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3860.814508941813</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>9.603333333333333</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4475,28 +4503,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4866</v>
+        <v>2232</v>
       </c>
       <c r="E8" t="n">
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>480.99</v>
+        <v>231.75</v>
       </c>
       <c r="G8" t="n">
-        <v>18048.725</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4508,28 +4536,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4866</v>
+        <v>5981</v>
       </c>
       <c r="E9" t="n">
-        <v>187</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>480.99</v>
+        <v>764.28</v>
       </c>
       <c r="G9" t="n">
-        <v>18048.725</v>
+        <v>2329.66</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4541,525 +4569,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2196</v>
+        <v>11102</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>297.6666666666667</v>
+        <v>1034.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4237.57</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B0DQ1NV8D2</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2196</v>
-      </c>
-      <c r="E11" t="n">
-        <v>36</v>
-      </c>
-      <c r="F11" t="n">
-        <v>297.6666666666667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4237.57</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B0DQ4YWSMC</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2196</v>
-      </c>
-      <c r="E12" t="n">
-        <v>36</v>
-      </c>
-      <c r="F12" t="n">
-        <v>297.6666666666667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4237.57</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B0BFVMDJ2K</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1942</v>
-      </c>
-      <c r="E13" t="n">
-        <v>57</v>
-      </c>
-      <c r="F13" t="n">
-        <v>321.02</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5306.565</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B0BFVNS8HS</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1942</v>
-      </c>
-      <c r="E14" t="n">
-        <v>57</v>
-      </c>
-      <c r="F14" t="n">
-        <v>321.02</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5306.565</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B0BFW59TRG</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1942</v>
-      </c>
-      <c r="E15" t="n">
-        <v>57</v>
-      </c>
-      <c r="F15" t="n">
-        <v>321.02</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5306.565</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B0BFWD6SNF</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1942</v>
-      </c>
-      <c r="E16" t="n">
-        <v>57</v>
-      </c>
-      <c r="F16" t="n">
-        <v>321.02</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5306.565</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>5925</v>
-      </c>
-      <c r="E17" t="n">
-        <v>67</v>
-      </c>
-      <c r="F17" t="n">
-        <v>655.9400000000001</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10810</v>
-      </c>
-      <c r="E18" t="n">
-        <v>142</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1717.92</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5567.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2366</v>
-      </c>
-      <c r="E19" t="n">
-        <v>19</v>
-      </c>
-      <c r="F19" t="n">
-        <v>203.86</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>16</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6.922404316345447</v>
-      </c>
-      <c r="G20" t="n">
-        <v>949.1964943859526</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>23</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10.06759568365455</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1380.463505614047</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>9690</v>
-      </c>
-      <c r="E22" t="n">
-        <v>92</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1496.6</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4955.93</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2180</v>
-      </c>
-      <c r="E23" t="n">
-        <v>19</v>
-      </c>
-      <c r="F23" t="n">
-        <v>231.75</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2880</v>
-      </c>
-      <c r="E24" t="n">
-        <v>34</v>
-      </c>
-      <c r="F24" t="n">
-        <v>386.03</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>6498</v>
-      </c>
-      <c r="E25" t="n">
-        <v>52</v>
-      </c>
-      <c r="F25" t="n">
-        <v>580.3499999999999</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4305,28 +4305,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8068</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>922.1800000000001</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>2626.28</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4338,28 +4338,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13719</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>187</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2366.55</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>8351.700000000001</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4371,22 +4371,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8961</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>918.96</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4404,28 +4404,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>19.6</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>4659.32</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4437,28 +4437,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6145</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>937.2172168694875</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>3424.775491058187</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4470,28 +4470,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6928</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1056.542783130512</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>3860.814508941813</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4503,28 +4503,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2232</v>
+        <v>6246</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>231</v>
       </c>
       <c r="F8" t="n">
-        <v>231.75</v>
+        <v>638.1221465443396</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>21941.73396743233</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4536,28 +4536,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5981</v>
+        <v>6105</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>226</v>
       </c>
       <c r="F9" t="n">
-        <v>764.28</v>
+        <v>623.6178534556605</v>
       </c>
       <c r="G9" t="n">
-        <v>2329.66</v>
+        <v>21443.00603256767</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4569,30 +4569,459 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8497</v>
+      </c>
+      <c r="E10" t="n">
+        <v>131</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1104.94</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25425.42</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E11" t="n">
+        <v>76</v>
+      </c>
+      <c r="F11" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76</v>
+      </c>
+      <c r="F12" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E13" t="n">
+        <v>76</v>
+      </c>
+      <c r="F13" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E14" t="n">
+        <v>76</v>
+      </c>
+      <c r="F14" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8068</v>
+      </c>
+      <c r="E15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" t="n">
+        <v>922.1800000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2626.28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13719</v>
+      </c>
+      <c r="E16" t="n">
+        <v>187</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2366.55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8351.700000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8961</v>
+      </c>
+      <c r="E17" t="n">
+        <v>79</v>
+      </c>
+      <c r="F17" t="n">
+        <v>918.96</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>47</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6145</v>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>937.2172168694875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3424.775491058187</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6928</v>
+      </c>
+      <c r="E20" t="n">
+        <v>61</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1056.542783130512</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3860.814508941813</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2232</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5981</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71</v>
+      </c>
+      <c r="F22" t="n">
+        <v>764.28</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D23" t="n">
         <v>11102</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E23" t="n">
         <v>92</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F23" t="n">
         <v>1034.6</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>19.6</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>4659.32</v>
+        <v>776.5533333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4866,28 +4866,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6145</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>937.2172168694875</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>3424.775491058187</v>
+        <v>776.5533333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4899,28 +4899,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6928</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1056.542783130512</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>3860.814508941813</v>
+        <v>776.5533333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -4932,25 +4932,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2232</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>231.75</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>776.5533333333333</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -4965,28 +4965,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5981</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>764.28</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>2329.66</v>
+        <v>776.5533333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4998,30 +4998,162 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>776.5533333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13073</v>
+      </c>
+      <c r="E24" t="n">
+        <v>116</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1993.76</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7285.59</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2232</v>
+      </c>
+      <c r="E25" t="n">
+        <v>19</v>
+      </c>
+      <c r="F25" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5981</v>
+      </c>
+      <c r="E26" t="n">
+        <v>71</v>
+      </c>
+      <c r="F26" t="n">
+        <v>764.28</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D27" t="n">
         <v>11102</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E27" t="n">
         <v>92</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F27" t="n">
         <v>1034.6</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>3.266666666666667</v>
+        <v>19.6</v>
       </c>
       <c r="G18" t="n">
-        <v>776.5533333333333</v>
+        <v>4659.32</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4866,28 +4866,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6145</v>
       </c>
       <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>937.2172168694875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3424.775491058187</v>
+      </c>
+      <c r="H19" t="n">
         <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="G19" t="n">
-        <v>776.5533333333333</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4899,28 +4899,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>6928</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
-        <v>3.266666666666667</v>
+        <v>1056.542783130512</v>
       </c>
       <c r="G20" t="n">
-        <v>776.5533333333333</v>
+        <v>3860.814508941813</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -4932,25 +4932,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>2232</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>3.266666666666667</v>
+        <v>231.75</v>
       </c>
       <c r="G21" t="n">
-        <v>776.5533333333333</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -4965,28 +4965,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>5981</v>
       </c>
       <c r="E22" t="n">
+        <v>71</v>
+      </c>
+      <c r="F22" t="n">
+        <v>764.28</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H22" t="n">
         <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="G22" t="n">
-        <v>776.5533333333333</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4998,162 +4998,30 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>11102</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="F23" t="n">
-        <v>3.266666666666667</v>
+        <v>1034.6</v>
       </c>
       <c r="G23" t="n">
-        <v>776.5533333333333</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>13073</v>
-      </c>
-      <c r="E24" t="n">
-        <v>116</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1993.76</v>
-      </c>
-      <c r="G24" t="n">
-        <v>7285.59</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2232</v>
-      </c>
-      <c r="E25" t="n">
-        <v>19</v>
-      </c>
-      <c r="F25" t="n">
-        <v>231.75</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>5981</v>
-      </c>
-      <c r="E26" t="n">
-        <v>71</v>
-      </c>
-      <c r="F26" t="n">
-        <v>764.28</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2329.66</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11102</v>
-      </c>
-      <c r="E27" t="n">
-        <v>92</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1034.6</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4508,20 +4508,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6246</v>
+        <v>6176</v>
       </c>
       <c r="E8" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F8" t="n">
-        <v>638.1221465443396</v>
+        <v>630.87</v>
       </c>
       <c r="G8" t="n">
-        <v>21941.73396743233</v>
+        <v>21692.37</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -4545,16 +4545,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6105</v>
+        <v>6176</v>
       </c>
       <c r="E9" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F9" t="n">
-        <v>623.6178534556605</v>
+        <v>630.87</v>
       </c>
       <c r="G9" t="n">
-        <v>21443.00603256767</v>
+        <v>21692.37</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -4574,23 +4574,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8497</v>
+        <v>2832</v>
       </c>
       <c r="E10" t="n">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="F10" t="n">
-        <v>1104.94</v>
+        <v>368.3133333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>25425.42</v>
+        <v>8475.139999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4602,28 +4602,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2674</v>
+        <v>2832</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>439.3</v>
+        <v>368.3133333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>3537.71</v>
+        <v>8475.139999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -4635,28 +4635,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2674</v>
+        <v>2832</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>439.3</v>
+        <v>368.3133333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>3537.71</v>
+        <v>8475.139999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -4734,28 +4734,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8068</v>
+        <v>2674</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
-        <v>922.1800000000001</v>
+        <v>439.3</v>
       </c>
       <c r="G15" t="n">
-        <v>2626.28</v>
+        <v>3537.71</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4767,28 +4767,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13719</v>
+        <v>2674</v>
       </c>
       <c r="E16" t="n">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="F16" t="n">
-        <v>2366.55</v>
+        <v>439.3</v>
       </c>
       <c r="G16" t="n">
-        <v>8351.700000000001</v>
+        <v>3537.71</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -4800,28 +4800,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8961</v>
+        <v>8068</v>
       </c>
       <c r="E17" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>918.96</v>
+        <v>922.1800000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2626.28</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -4833,28 +4833,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>13719</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="F18" t="n">
-        <v>19.6</v>
+        <v>2366.55</v>
       </c>
       <c r="G18" t="n">
-        <v>4659.32</v>
+        <v>8351.700000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4875,19 +4875,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6145</v>
+        <v>8961</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="F19" t="n">
-        <v>937.2172168694875</v>
+        <v>918.96</v>
       </c>
       <c r="G19" t="n">
-        <v>3424.775491058187</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4899,28 +4899,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6928</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1056.542783130512</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>3860.814508941813</v>
+        <v>776.5533333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -4932,25 +4932,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2232</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>231.75</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>776.5533333333333</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -4965,28 +4965,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5981</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>764.28</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>2329.66</v>
+        <v>776.5533333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4998,30 +4998,228 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>776.5533333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>776.5533333333333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="G25" t="n">
+        <v>776.5533333333333</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13073</v>
+      </c>
+      <c r="E26" t="n">
+        <v>116</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1993.76</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7285.59</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2232</v>
+      </c>
+      <c r="E27" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5981</v>
+      </c>
+      <c r="E28" t="n">
+        <v>71</v>
+      </c>
+      <c r="F28" t="n">
+        <v>764.28</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D29" t="n">
         <v>11102</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E29" t="n">
         <v>92</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F29" t="n">
         <v>1034.6</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -996,7 +996,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF- Phrase</t>
+          <t>Camb-SP- L Shape-B0BFWD6SNF- Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1024,7 +1024,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-BM</t>
+          <t>Camb-SP- L Shape-B0BFWD6SNF-BM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1052,7 +1052,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact</t>
+          <t>Camb-SP- L Shape-B0BFWD6SNF-Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1080,7 +1080,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-PT</t>
+          <t>Camb-SP- L Shape-B0BFWD6SNF-PT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1291,7 +1291,7 @@
         <v>99</v>
       </c>
       <c r="F31" t="n">
-        <v>13656</v>
+        <v>13654</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>80</v>
       </c>
       <c r="F37" t="n">
-        <v>22616</v>
+        <v>22615</v>
       </c>
       <c r="G37" t="n">
         <v>7075.42</v>
@@ -1711,7 +1711,7 @@
         <v>153</v>
       </c>
       <c r="F46" t="n">
-        <v>20137</v>
+        <v>20133</v>
       </c>
       <c r="G46" t="n">
         <v>21777.12</v>
@@ -2775,7 +2775,7 @@
         <v>150</v>
       </c>
       <c r="F84" t="n">
-        <v>32623</v>
+        <v>32622</v>
       </c>
       <c r="G84" t="n">
         <v>11648.3</v>
@@ -3279,7 +3279,7 @@
         <v>66</v>
       </c>
       <c r="F102" t="n">
-        <v>14024</v>
+        <v>14022</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4578,16 +4578,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2832</v>
+        <v>4248</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
-        <v>368.3133333333333</v>
+        <v>552.47</v>
       </c>
       <c r="G10" t="n">
-        <v>8475.139999999999</v>
+        <v>12712.71</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -4607,20 +4607,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2832</v>
+        <v>4248</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>368.3133333333333</v>
+        <v>552.47</v>
       </c>
       <c r="G11" t="n">
-        <v>8475.139999999999</v>
+        <v>12712.71</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -4635,28 +4635,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2832</v>
+        <v>2674</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
-        <v>368.3133333333333</v>
+        <v>439.3</v>
       </c>
       <c r="G12" t="n">
-        <v>8475.139999999999</v>
+        <v>3537.71</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -4767,28 +4767,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2674</v>
+        <v>8068</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>439.3</v>
+        <v>922.1800000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>3537.71</v>
+        <v>2626.28</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -4800,28 +4800,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8068</v>
+        <v>13719</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="F17" t="n">
-        <v>922.1800000000001</v>
+        <v>2366.55</v>
       </c>
       <c r="G17" t="n">
-        <v>2626.28</v>
+        <v>8351.700000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -4833,28 +4833,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13719</v>
+        <v>8961</v>
       </c>
       <c r="E18" t="n">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="F18" t="n">
-        <v>2366.55</v>
+        <v>918.96</v>
       </c>
       <c r="G18" t="n">
-        <v>8351.700000000001</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4875,19 +4875,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8961</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>918.96</v>
+        <v>19.6</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4659.32</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4908,19 +4908,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>6145</v>
       </c>
       <c r="E20" t="n">
+        <v>55</v>
+      </c>
+      <c r="F20" t="n">
+        <v>937.2172168694875</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3424.775491058187</v>
+      </c>
+      <c r="H20" t="n">
         <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="G20" t="n">
-        <v>776.5533333333333</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -4932,28 +4932,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6928</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F21" t="n">
-        <v>3.266666666666667</v>
+        <v>1056.542783130512</v>
       </c>
       <c r="G21" t="n">
-        <v>776.5533333333333</v>
+        <v>3860.814508941813</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4965,25 +4965,25 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>2232</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F22" t="n">
-        <v>3.266666666666667</v>
+        <v>231.75</v>
       </c>
       <c r="G22" t="n">
-        <v>776.5533333333333</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -4998,28 +4998,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>5981</v>
       </c>
       <c r="E23" t="n">
+        <v>71</v>
+      </c>
+      <c r="F23" t="n">
+        <v>764.28</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H23" t="n">
         <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="G23" t="n">
-        <v>776.5533333333333</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -5031,195 +5031,30 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>11102</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="F24" t="n">
-        <v>3.266666666666667</v>
+        <v>1034.6</v>
       </c>
       <c r="G24" t="n">
-        <v>776.5533333333333</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="G25" t="n">
-        <v>776.5533333333333</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>13073</v>
-      </c>
-      <c r="E26" t="n">
-        <v>116</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1993.76</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7285.59</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2232</v>
-      </c>
-      <c r="E27" t="n">
-        <v>19</v>
-      </c>
-      <c r="F27" t="n">
-        <v>231.75</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>5981</v>
-      </c>
-      <c r="E28" t="n">
-        <v>71</v>
-      </c>
-      <c r="F28" t="n">
-        <v>764.28</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2329.66</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11102</v>
-      </c>
-      <c r="E29" t="n">
-        <v>92</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1034.6</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -535,7 +535,7 @@
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>10060</v>
+        <v>10059</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -660,7 +660,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-KT-Phrase</t>
+          <t>Camb-L shape-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -688,7 +688,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-Lshape-SP-KT-Phrase</t>
+          <t>Camb-L shape-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -787,7 +787,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -815,7 +815,7 @@
         <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>43</v>
       </c>
       <c r="F24" t="n">
-        <v>5864</v>
+        <v>5859</v>
       </c>
       <c r="G24" t="n">
         <v>21607.62</v>
@@ -1276,7 +1276,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
+          <t>Camb-SP-L shape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1304,7 +1304,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
+          <t>Camb-SP-L shape-B0BFWD6SNF - Broad</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-SP-L shape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1360,7 +1360,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-L shape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1369,125 +1369,125 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>593.87</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5972</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-L shape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2653.69</v>
+        <v>1791.87</v>
       </c>
       <c r="E35" t="n">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="F35" t="n">
-        <v>44557</v>
+        <v>22615</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-L shape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>593.87</v>
+        <v>245.5</v>
       </c>
       <c r="E36" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>5972</v>
+        <v>4641</v>
       </c>
       <c r="G36" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1791.87</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>22615</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>245.5</v>
+        <v>2653.69</v>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="F38" t="n">
-        <v>4641</v>
+        <v>44557</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>95</v>
       </c>
       <c r="F39" t="n">
-        <v>11996</v>
+        <v>11992</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>13</v>
       </c>
       <c r="F41" t="n">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>41</v>
       </c>
       <c r="F42" t="n">
-        <v>4911</v>
+        <v>4907</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         <v>12768</v>
       </c>
       <c r="G50" t="n">
-        <v>7287.29</v>
+        <v>14574.58</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>987.9399999999999</v>
+        <v>961.65</v>
       </c>
       <c r="E76" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F76" t="n">
-        <v>8743</v>
+        <v>8741</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>3930</v>
+        <v>3928</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>3369</v>
+        <v>3366</v>
       </c>
       <c r="G89" t="n">
         <v>1694.07</v>
@@ -3251,7 +3251,7 @@
         <v>47</v>
       </c>
       <c r="F101" t="n">
-        <v>7144</v>
+        <v>7143</v>
       </c>
       <c r="G101" t="n">
         <v>4744.06</v>
@@ -3450,10 +3450,10 @@
         <v>4841</v>
       </c>
       <c r="G108" t="n">
-        <v>2580.52</v>
+        <v>3071.2</v>
       </c>
       <c r="H108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
@@ -4119,7 +4119,7 @@
         <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>23410</v>
+        <v>23409</v>
       </c>
       <c r="G11" t="n">
         <v>1450.85</v>
@@ -4231,7 +4231,7 @@
         <v>97</v>
       </c>
       <c r="F15" t="n">
-        <v>30782</v>
+        <v>30781</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4305,28 +4305,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>8068</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>10.96333333333333</v>
+        <v>922.1800000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2626.28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4338,28 +4338,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>13719</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="F3" t="n">
-        <v>10.96333333333333</v>
+        <v>2366.55</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>8351.700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4371,22 +4371,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>8961</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>10.96333333333333</v>
+        <v>918.96</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4404,28 +4404,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10.96333333333333</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4437,28 +4437,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>6145</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>10.96333333333333</v>
+        <v>937.2172168694875</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3424.775491058187</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4470,28 +4470,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>6928</v>
       </c>
       <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1056.542783130512</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3860.814508941813</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10.96333333333333</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4503,28 +4503,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6176</v>
+        <v>2232</v>
       </c>
       <c r="E8" t="n">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>630.87</v>
+        <v>231.75</v>
       </c>
       <c r="G8" t="n">
-        <v>21692.37</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4536,28 +4536,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6176</v>
+        <v>5981</v>
       </c>
       <c r="E9" t="n">
-        <v>228</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>630.87</v>
+        <v>764.28</v>
       </c>
       <c r="G9" t="n">
-        <v>21692.37</v>
+        <v>2329.66</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4569,492 +4569,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4248</v>
+        <v>11102</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>552.47</v>
+        <v>1034.6</v>
       </c>
       <c r="G10" t="n">
-        <v>12712.71</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B0DQ4YWSMC</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4248</v>
-      </c>
-      <c r="E11" t="n">
-        <v>66</v>
-      </c>
-      <c r="F11" t="n">
-        <v>552.47</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12712.71</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B0BFVMDJ2K</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E12" t="n">
-        <v>76</v>
-      </c>
-      <c r="F12" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B0BFVNS8HS</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E13" t="n">
-        <v>76</v>
-      </c>
-      <c r="F13" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B0BFW59TRG</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E14" t="n">
-        <v>76</v>
-      </c>
-      <c r="F14" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B0BFWD6SNF</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E15" t="n">
-        <v>76</v>
-      </c>
-      <c r="F15" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>8068</v>
-      </c>
-      <c r="E16" t="n">
-        <v>90</v>
-      </c>
-      <c r="F16" t="n">
-        <v>922.1800000000001</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2626.28</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>13719</v>
-      </c>
-      <c r="E17" t="n">
-        <v>187</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2366.55</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8351.700000000001</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>8961</v>
-      </c>
-      <c r="E18" t="n">
-        <v>79</v>
-      </c>
-      <c r="F18" t="n">
-        <v>918.96</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>47</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4659.32</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>6145</v>
-      </c>
-      <c r="E20" t="n">
-        <v>55</v>
-      </c>
-      <c r="F20" t="n">
-        <v>937.2172168694875</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3424.775491058187</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>6928</v>
-      </c>
-      <c r="E21" t="n">
-        <v>61</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1056.542783130512</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3860.814508941813</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2232</v>
-      </c>
-      <c r="E22" t="n">
-        <v>19</v>
-      </c>
-      <c r="F22" t="n">
-        <v>231.75</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>5981</v>
-      </c>
-      <c r="E23" t="n">
-        <v>71</v>
-      </c>
-      <c r="F23" t="n">
-        <v>764.28</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2329.66</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11102</v>
-      </c>
-      <c r="E24" t="n">
-        <v>92</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1034.6</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4305,28 +4305,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8068</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>922.1800000000001</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>2626.28</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4338,28 +4338,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13719</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>187</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2366.55</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>8351.700000000001</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4371,22 +4371,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8961</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>918.96</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4404,28 +4404,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>19.6</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>4659.32</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4437,28 +4437,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6145</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>937.2172168694875</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>3424.775491058187</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4470,28 +4470,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6928</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1056.542783130512</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>3860.814508941813</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4503,28 +4503,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2232</v>
+        <v>6244</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>231</v>
       </c>
       <c r="F8" t="n">
-        <v>231.75</v>
+        <v>637.8591577223928</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>21941.73396743233</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4536,28 +4536,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5981</v>
+        <v>6102</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>226</v>
       </c>
       <c r="F9" t="n">
-        <v>764.28</v>
+        <v>623.3608422776073</v>
       </c>
       <c r="G9" t="n">
-        <v>2329.66</v>
+        <v>21443.00603256767</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4569,30 +4569,459 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8497</v>
+      </c>
+      <c r="E10" t="n">
+        <v>131</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1104.94</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25425.42</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E11" t="n">
+        <v>76</v>
+      </c>
+      <c r="F11" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76</v>
+      </c>
+      <c r="F12" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E13" t="n">
+        <v>76</v>
+      </c>
+      <c r="F13" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E14" t="n">
+        <v>76</v>
+      </c>
+      <c r="F14" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8068</v>
+      </c>
+      <c r="E15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" t="n">
+        <v>922.1800000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2626.28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13719</v>
+      </c>
+      <c r="E16" t="n">
+        <v>187</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2366.55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8351.700000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8961</v>
+      </c>
+      <c r="E17" t="n">
+        <v>79</v>
+      </c>
+      <c r="F17" t="n">
+        <v>918.96</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>47</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6145</v>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>937.2172168694875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3424.775491058187</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6928</v>
+      </c>
+      <c r="E20" t="n">
+        <v>61</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1056.542783130512</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3860.814508941813</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2232</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5981</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71</v>
+      </c>
+      <c r="F22" t="n">
+        <v>764.28</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D23" t="n">
         <v>11102</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E23" t="n">
         <v>92</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F23" t="n">
         <v>1034.6</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -3338,10 +3338,10 @@
         <v>10609</v>
       </c>
       <c r="G104" t="n">
-        <v>2453.4</v>
+        <v>2816.96</v>
       </c>
       <c r="H104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4305,28 +4305,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>8068</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>10.96333333333333</v>
+        <v>922.1800000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2626.28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4338,28 +4338,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>13719</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="F3" t="n">
-        <v>10.96333333333333</v>
+        <v>2366.55</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>8351.700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4371,22 +4371,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>8961</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>10.96333333333333</v>
+        <v>918.96</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4404,28 +4404,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10.96333333333333</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4437,28 +4437,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>6145</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>10.96333333333333</v>
+        <v>937.2172168694875</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3424.775491058187</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4470,28 +4470,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>6928</v>
       </c>
       <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1056.542783130512</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3860.814508941813</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10.96333333333333</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4503,28 +4503,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6244</v>
+        <v>2232</v>
       </c>
       <c r="E8" t="n">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>637.8591577223928</v>
+        <v>231.75</v>
       </c>
       <c r="G8" t="n">
-        <v>21941.73396743233</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4536,28 +4536,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6102</v>
+        <v>5981</v>
       </c>
       <c r="E9" t="n">
-        <v>226</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>623.3608422776073</v>
+        <v>764.28</v>
       </c>
       <c r="G9" t="n">
-        <v>21443.00603256767</v>
+        <v>2329.66</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4569,459 +4569,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8497</v>
+        <v>11102</v>
       </c>
       <c r="E10" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>1104.94</v>
+        <v>1034.6</v>
       </c>
       <c r="G10" t="n">
-        <v>25425.42</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B0BFVMDJ2K</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E11" t="n">
-        <v>76</v>
-      </c>
-      <c r="F11" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B0BFVNS8HS</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E12" t="n">
-        <v>76</v>
-      </c>
-      <c r="F12" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B0BFW59TRG</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E13" t="n">
-        <v>76</v>
-      </c>
-      <c r="F13" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B0BFWD6SNF</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E14" t="n">
-        <v>76</v>
-      </c>
-      <c r="F14" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>8068</v>
-      </c>
-      <c r="E15" t="n">
-        <v>90</v>
-      </c>
-      <c r="F15" t="n">
-        <v>922.1800000000001</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2626.28</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>13719</v>
-      </c>
-      <c r="E16" t="n">
-        <v>187</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2366.55</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8351.700000000001</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>8961</v>
-      </c>
-      <c r="E17" t="n">
-        <v>79</v>
-      </c>
-      <c r="F17" t="n">
-        <v>918.96</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>47</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4659.32</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>6145</v>
-      </c>
-      <c r="E19" t="n">
-        <v>55</v>
-      </c>
-      <c r="F19" t="n">
-        <v>937.2172168694875</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3424.775491058187</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>6928</v>
-      </c>
-      <c r="E20" t="n">
-        <v>61</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1056.542783130512</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3860.814508941813</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>2232</v>
-      </c>
-      <c r="E21" t="n">
-        <v>19</v>
-      </c>
-      <c r="F21" t="n">
-        <v>231.75</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>5981</v>
-      </c>
-      <c r="E22" t="n">
-        <v>71</v>
-      </c>
-      <c r="F22" t="n">
-        <v>764.28</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2329.66</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11102</v>
-      </c>
-      <c r="E23" t="n">
-        <v>92</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1034.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4305,28 +4305,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8068</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>922.1800000000001</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>2626.28</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4338,28 +4338,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13719</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>187</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2366.55</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>8351.700000000001</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4371,22 +4371,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8961</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>918.96</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4404,28 +4404,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>19.6</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>4659.32</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4437,28 +4437,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6145</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>937.2172168694875</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>3424.775491058187</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4470,28 +4470,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6928</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1056.542783130512</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>3860.814508941813</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4503,28 +4503,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2232</v>
+        <v>6173</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="F8" t="n">
-        <v>231.75</v>
+        <v>630.61</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>21692.37</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4536,28 +4536,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5981</v>
+        <v>6173</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="F9" t="n">
-        <v>764.28</v>
+        <v>630.61</v>
       </c>
       <c r="G9" t="n">
-        <v>2329.66</v>
+        <v>21692.37</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4569,30 +4569,492 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4248</v>
+      </c>
+      <c r="E10" t="n">
+        <v>66</v>
+      </c>
+      <c r="F10" t="n">
+        <v>552.47</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12712.71</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4248</v>
+      </c>
+      <c r="E11" t="n">
+        <v>66</v>
+      </c>
+      <c r="F11" t="n">
+        <v>552.47</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12712.71</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76</v>
+      </c>
+      <c r="F12" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E13" t="n">
+        <v>76</v>
+      </c>
+      <c r="F13" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E14" t="n">
+        <v>76</v>
+      </c>
+      <c r="F14" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E15" t="n">
+        <v>76</v>
+      </c>
+      <c r="F15" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8068</v>
+      </c>
+      <c r="E16" t="n">
+        <v>90</v>
+      </c>
+      <c r="F16" t="n">
+        <v>922.1800000000001</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2626.28</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13719</v>
+      </c>
+      <c r="E17" t="n">
+        <v>187</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2366.55</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8351.700000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8961</v>
+      </c>
+      <c r="E18" t="n">
+        <v>79</v>
+      </c>
+      <c r="F18" t="n">
+        <v>918.96</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>47</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6145</v>
+      </c>
+      <c r="E20" t="n">
+        <v>55</v>
+      </c>
+      <c r="F20" t="n">
+        <v>937.2172168694875</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3424.775491058187</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6928</v>
+      </c>
+      <c r="E21" t="n">
+        <v>61</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1056.542783130512</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3860.814508941813</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2232</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5981</v>
+      </c>
+      <c r="E23" t="n">
+        <v>71</v>
+      </c>
+      <c r="F23" t="n">
+        <v>764.28</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D24" t="n">
         <v>11102</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E24" t="n">
         <v>92</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F24" t="n">
         <v>1034.6</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -2439,7 +2439,7 @@
         <v>42</v>
       </c>
       <c r="F72" t="n">
-        <v>9391</v>
+        <v>9389</v>
       </c>
       <c r="G72" t="n">
         <v>2783.9</v>
@@ -2495,7 +2495,7 @@
         <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>16197</v>
+        <v>16194</v>
       </c>
       <c r="G74" t="n">
         <v>2783.9</v>
@@ -2691,7 +2691,7 @@
         <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>66</v>
       </c>
       <c r="F82" t="n">
-        <v>15066</v>
+        <v>15065</v>
       </c>
       <c r="G82" t="n">
         <v>6703.389999999999</v>
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4305,28 +4305,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>8068</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>10.96333333333333</v>
+        <v>922.1800000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2626.28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4338,28 +4338,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>13719</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="F3" t="n">
-        <v>10.96333333333333</v>
+        <v>2366.55</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>8351.700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4371,22 +4371,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>8961</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>10.96333333333333</v>
+        <v>918.96</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4404,28 +4404,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10.96333333333333</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4437,28 +4437,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>6145</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>10.96333333333333</v>
+        <v>937.2172168694875</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3424.775491058187</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4470,28 +4470,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>6928</v>
       </c>
       <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1056.542783130512</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3860.814508941813</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10.96333333333333</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4503,28 +4503,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6173</v>
+        <v>2232</v>
       </c>
       <c r="E8" t="n">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>630.61</v>
+        <v>231.75</v>
       </c>
       <c r="G8" t="n">
-        <v>21692.37</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4536,28 +4536,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6173</v>
+        <v>5981</v>
       </c>
       <c r="E9" t="n">
-        <v>228</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>630.61</v>
+        <v>764.28</v>
       </c>
       <c r="G9" t="n">
-        <v>21692.37</v>
+        <v>2329.66</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4569,492 +4569,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4248</v>
+        <v>11102</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>552.47</v>
+        <v>1034.6</v>
       </c>
       <c r="G10" t="n">
-        <v>12712.71</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B0DQ4YWSMC</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4248</v>
-      </c>
-      <c r="E11" t="n">
-        <v>66</v>
-      </c>
-      <c r="F11" t="n">
-        <v>552.47</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12712.71</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B0BFVMDJ2K</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E12" t="n">
-        <v>76</v>
-      </c>
-      <c r="F12" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B0BFVNS8HS</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E13" t="n">
-        <v>76</v>
-      </c>
-      <c r="F13" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B0BFW59TRG</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E14" t="n">
-        <v>76</v>
-      </c>
-      <c r="F14" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B0BFWD6SNF</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2674</v>
-      </c>
-      <c r="E15" t="n">
-        <v>76</v>
-      </c>
-      <c r="F15" t="n">
-        <v>439.3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3537.71</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>8068</v>
-      </c>
-      <c r="E16" t="n">
-        <v>90</v>
-      </c>
-      <c r="F16" t="n">
-        <v>922.1800000000001</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2626.28</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>13719</v>
-      </c>
-      <c r="E17" t="n">
-        <v>187</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2366.55</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8351.700000000001</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>8961</v>
-      </c>
-      <c r="E18" t="n">
-        <v>79</v>
-      </c>
-      <c r="F18" t="n">
-        <v>918.96</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>47</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4659.32</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>6145</v>
-      </c>
-      <c r="E20" t="n">
-        <v>55</v>
-      </c>
-      <c r="F20" t="n">
-        <v>937.2172168694875</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3424.775491058187</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>6928</v>
-      </c>
-      <c r="E21" t="n">
-        <v>61</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1056.542783130512</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3860.814508941813</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2232</v>
-      </c>
-      <c r="E22" t="n">
-        <v>19</v>
-      </c>
-      <c r="F22" t="n">
-        <v>231.75</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>5981</v>
-      </c>
-      <c r="E23" t="n">
-        <v>71</v>
-      </c>
-      <c r="F23" t="n">
-        <v>764.28</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2329.66</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11102</v>
-      </c>
-      <c r="E24" t="n">
-        <v>92</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1034.6</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week24.xlsx
@@ -479,7 +479,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>135</v>
       </c>
       <c r="F18" t="n">
-        <v>30841</v>
+        <v>30840</v>
       </c>
       <c r="G18" t="n">
         <v>12712.71</v>
@@ -1487,7 +1487,7 @@
         <v>131</v>
       </c>
       <c r="F38" t="n">
-        <v>44557</v>
+        <v>44556</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2096.32</v>
+        <v>2085.55</v>
       </c>
       <c r="E45" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F45" t="n">
-        <v>10523</v>
+        <v>10521</v>
       </c>
       <c r="G45" t="n">
         <v>14489.83</v>
@@ -4251,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4305,28 +4305,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8068</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>922.1800000000001</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>2626.28</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4338,28 +4338,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13719</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>187</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2366.55</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>8351.700000000001</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4371,22 +4371,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8961</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>918.96</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4404,28 +4404,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>19.6</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>4659.32</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4437,28 +4437,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6145</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>937.2172168694875</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>3424.775491058187</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4470,28 +4470,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6928</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1056.542783130512</v>
+        <v>10.96333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>3860.814508941813</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4503,28 +4503,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2232</v>
+        <v>6244</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>231</v>
       </c>
       <c r="F8" t="n">
-        <v>231.75</v>
+        <v>637.8591577223928</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>21941.73396743233</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4536,28 +4536,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5981</v>
+        <v>6102</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>226</v>
       </c>
       <c r="F9" t="n">
-        <v>764.28</v>
+        <v>623.3608422776073</v>
       </c>
       <c r="G9" t="n">
-        <v>2329.66</v>
+        <v>21443.00603256767</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4569,30 +4569,459 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8497</v>
+      </c>
+      <c r="E10" t="n">
+        <v>131</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1104.94</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25425.42</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E11" t="n">
+        <v>76</v>
+      </c>
+      <c r="F11" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76</v>
+      </c>
+      <c r="F12" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E13" t="n">
+        <v>76</v>
+      </c>
+      <c r="F13" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E14" t="n">
+        <v>76</v>
+      </c>
+      <c r="F14" t="n">
+        <v>439.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3537.71</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8068</v>
+      </c>
+      <c r="E15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" t="n">
+        <v>922.1800000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2626.28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13719</v>
+      </c>
+      <c r="E16" t="n">
+        <v>187</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2366.55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8351.700000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8961</v>
+      </c>
+      <c r="E17" t="n">
+        <v>79</v>
+      </c>
+      <c r="F17" t="n">
+        <v>918.96</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>47</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6145</v>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>937.2172168694875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3424.775491058187</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6928</v>
+      </c>
+      <c r="E20" t="n">
+        <v>61</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1056.542783130512</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3860.814508941813</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2232</v>
+      </c>
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5981</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71</v>
+      </c>
+      <c r="F22" t="n">
+        <v>764.28</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D23" t="n">
         <v>11102</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E23" t="n">
         <v>92</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F23" t="n">
         <v>1034.6</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>
